--- a/static/excel/INTC_model.xlsx
+++ b/static/excel/INTC_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
     <numFmt numFmtId="175" formatCode="0.000"/>
     <numFmt numFmtId="176" formatCode="0.00;(0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -223,12 +223,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B5E20"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00E65100"/>
       <sz val="10"/>
     </font>
@@ -244,7 +238,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -341,11 +335,6 @@
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -373,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -769,10 +758,7 @@
     <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -785,17 +771,17 @@
     <xf numFmtId="0" fontId="30" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="33" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="32" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -7353,11 +7339,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>582664.1800000001</v>
+        <v>602315.84</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $115.93</t>
+          <t>FMP marketCap  |  price $119.84</t>
         </is>
       </c>
     </row>
@@ -7439,11 +7425,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7440,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7526,7 +7512,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.152</v>
+        <v>1.151</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7736,11 +7722,11 @@
         </is>
       </c>
       <c r="B37" s="46" t="n">
-        <v>0.1646</v>
+        <v>0.1657</v>
       </c>
       <c r="C37" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 12.00%</t>
+          <t>Rf 4.57% + spread 12.00%</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7752,7 @@
         </is>
       </c>
       <c r="B39" s="48" t="n">
-        <v>0.0936</v>
+        <v>0.0941</v>
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
@@ -7831,16 +7817,16 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="55" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B46" s="56">
-        <f>B8*B30+B9*B39*(1-B43)</f>
+        <f>MAX(0.085, B8*B30+B9*B39*(1-B43))</f>
         <v/>
       </c>
       <c r="C46" s="57" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8204,13 +8190,13 @@
         <v/>
       </c>
       <c r="G7" s="72" t="n">
-        <v>0.1034</v>
+        <v>0.1038</v>
       </c>
       <c r="H7" s="72" t="n">
-        <v>0.1055</v>
+        <v>0.1067</v>
       </c>
       <c r="I7" s="72" t="n">
-        <v>0.1014</v>
+        <v>0.1048</v>
       </c>
       <c r="J7" s="73">
         <f>I7</f>
@@ -8554,13 +8540,13 @@
         <v/>
       </c>
       <c r="G15" s="78" t="n">
-        <v>58316.4</v>
+        <v>58341.5</v>
       </c>
       <c r="H15" s="78" t="n">
-        <v>64466.9</v>
+        <v>64566.6</v>
       </c>
       <c r="I15" s="78" t="n">
-        <v>71004.60000000001</v>
+        <v>71330.7</v>
       </c>
       <c r="J15" s="79">
         <f>I15*(1+J7)</f>
@@ -8588,27 +8574,27 @@
       </c>
       <c r="G16" s="83" t="inlineStr">
         <is>
-          <t>53,943 — 60,256</t>
+          <t>53,957 — 60,271</t>
         </is>
       </c>
       <c r="H16" s="83" t="inlineStr">
         <is>
-          <t>57,373 — 72,143</t>
+          <t>57,407 — 72,186</t>
         </is>
       </c>
       <c r="I16" s="83" t="inlineStr">
         <is>
-          <t>70,821 — 71,189</t>
+          <t>71,278 — 71,383</t>
         </is>
       </c>
       <c r="J16" s="83" t="inlineStr">
         <is>
-          <t>70,123 — 85,732</t>
+          <t>70,075 — 85,673</t>
         </is>
       </c>
       <c r="K16" s="83" t="inlineStr">
         <is>
-          <t>97,702 — 119,451</t>
+          <t>97,636 — 119,369</t>
         </is>
       </c>
       <c r="L16" s="84" t="inlineStr">
@@ -8752,13 +8738,13 @@
         <v/>
       </c>
       <c r="G20" s="78" t="n">
-        <v>14789</v>
+        <v>14795.3</v>
       </c>
       <c r="H20" s="78" t="n">
-        <v>16348.7</v>
+        <v>16374</v>
       </c>
       <c r="I20" s="78" t="n">
-        <v>18006.7</v>
+        <v>18089.4</v>
       </c>
       <c r="J20" s="79">
         <f>J15*J8</f>
@@ -8786,27 +8772,27 @@
       </c>
       <c r="G21" s="83" t="inlineStr">
         <is>
-          <t>13,680 — 15,281</t>
+          <t>13,683 — 15,285</t>
         </is>
       </c>
       <c r="H21" s="83" t="inlineStr">
         <is>
-          <t>14,550 — 18,295</t>
+          <t>14,558 — 18,306</t>
         </is>
       </c>
       <c r="I21" s="83" t="inlineStr">
         <is>
-          <t>17,960 — 18,053</t>
+          <t>18,076 — 18,103</t>
         </is>
       </c>
       <c r="J21" s="83" t="inlineStr">
         <is>
-          <t>17,783 — 21,741</t>
+          <t>17,771 — 21,727</t>
         </is>
       </c>
       <c r="K21" s="83" t="inlineStr">
         <is>
-          <t>24,777 — 30,292</t>
+          <t>24,760 — 30,272</t>
         </is>
       </c>
       <c r="L21" s="84" t="inlineStr">
@@ -9986,7 +9972,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>115.93</v>
+        <v>119.84</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10070,7 +10056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10086,7 +10072,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — INTC  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — INTC  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10171,7 @@
         </is>
       </c>
       <c r="C8" s="121" t="n">
-        <v>0.025</v>
+        <v>0.075</v>
       </c>
       <c r="D8" s="122" t="inlineStr">
         <is>
@@ -10215,11 +10201,11 @@
         </is>
       </c>
       <c r="C9" s="129" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D9" s="130" t="inlineStr">
         <is>
-          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -1.1% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
+          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -13.1% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="131" t="inlineStr">
@@ -10236,7 +10222,7 @@
       </c>
       <c r="H9" s="134" t="inlineStr">
         <is>
-          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -1.1% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
+          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -13.1% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10238,7 @@
         </is>
       </c>
       <c r="C10" s="121" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="D10" s="122" t="inlineStr">
         <is>
@@ -10282,11 +10268,11 @@
         </is>
       </c>
       <c r="C11" s="129" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="D11" s="130" t="inlineStr">
         <is>
-          <t>ROIC trend -1.7% ✓ (≥-2pp)  |  GM maintained -7.8% ✗  |  Op margin -3.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count +4.6%/yr ✗ (≤+2%/yr)  |  Goodwill/Equity 21% ✓ (&lt;40%)  [2/6 indicators positive — proxy score]</t>
+          <t>ROIC trend -1.7% ✓ (&gt;=-2pp)  |  GM maintained -7.8% ✗  |  Op margin -3.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count +4.6%/yr ✗ (≤+2%/yr)  |  Goodwill/Equity 21% ✓ (&lt;40%)  [2/6 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E11" s="131" t="inlineStr">
@@ -10303,7 +10289,7 @@
       </c>
       <c r="H11" s="134" t="inlineStr">
         <is>
-          <t>ROIC trend -1.7% ✓ (≥-2pp)  |  GM maintained -7.8% ✗  |  Op margin -3.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count +4.6%/yr ✗ (≤+2%/yr)  |  Goodwill/Equity 21% ✓ (&lt;40%)  [2/6 indicators positive — proxy score]</t>
+          <t>ROIC trend -1.7% ✓ (&gt;=-2pp)  |  GM maintained -7.8% ✗  |  Op margin -3.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count +4.6%/yr ✗ (≤+2%/yr)  |  Goodwill/Equity 21% ✓ (&lt;40%)  [2/6 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10312,7 @@
         </is>
       </c>
       <c r="C13" s="129" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="D13" s="130" t="inlineStr">
         <is>
@@ -10352,51 +10338,21 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cash Quality  (FCF / Net Income)</t>
-        </is>
-      </c>
-      <c r="B14" s="128" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C14" s="129" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="130" t="inlineStr">
-        <is>
-          <t>1311%  [through-cycle: 70/30 latest+5yr median, latest 1853.6% → smoothed 1311.3%]</t>
-        </is>
-      </c>
-      <c r="E14" s="135" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F14" s="132" t="n">
-        <v>12</v>
-      </c>
-      <c r="G14" s="133">
-        <f>IF(F14="",0,C14*F14*10)</f>
-        <v/>
-      </c>
-      <c r="H14" s="134" t="inlineStr">
-        <is>
-          <t>1311%  [through-cycle: 70/30 latest+5yr median, latest 1853.6% → smoothed 1311.3%]</t>
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>PART 3 — RISK PROFILE  (quantitative / qualitative)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capital Returns</t>
+          <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
         </is>
       </c>
       <c r="B15" s="128" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C15" s="129" t="n">
@@ -10404,16 +10360,16 @@
       </c>
       <c r="D15" s="130" t="inlineStr">
         <is>
-          <t>No capital returns in latest year</t>
-        </is>
-      </c>
-      <c r="E15" s="131" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>3.2x</t>
+        </is>
+      </c>
+      <c r="E15" s="135" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
         </is>
       </c>
       <c r="F15" s="132" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="G15" s="133">
         <f>IF(F15="",0,C15*F15*10)</f>
@@ -10421,36 +10377,36 @@
       </c>
       <c r="H15" s="134" t="inlineStr">
         <is>
-          <t>No capital returns in latest year</t>
+          <t>3.2x</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROIC</t>
+          <t xml:space="preserve">  Execution Risk</t>
         </is>
       </c>
       <c r="B16" s="128" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C16" s="129" t="n">
-        <v>0.075</v>
+        <v>0.05</v>
       </c>
       <c r="D16" s="130" t="inlineStr">
         <is>
-          <t>0.5%  [through-cycle: 70/30 latest+5yr median, latest 0.0% → smoothed 0.5%]  [QoE: CFO/NI -999% 3yr avg — cash conv weak]</t>
-        </is>
-      </c>
-      <c r="E16" s="131" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>Rev growth σ=8.2%  |  OM trend -24.6%, σ=10.9%  [quality = direction + stability]</t>
+        </is>
+      </c>
+      <c r="E16" s="135" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
         </is>
       </c>
       <c r="F16" s="132" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="G16" s="133">
         <f>IF(F16="",0,C16*F16*10)</f>
@@ -10458,301 +10414,101 @@
       </c>
       <c r="H16" s="134" t="inlineStr">
         <is>
-          <t>0.5%  [through-cycle: 70/30 latest+5yr median, latest 0.0% → smoothed 0.5%]  [QoE: CFO/NI -999% 3yr avg — cash conv weak]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>PART 3 — RISK PROFILE  (quantitative / qualitative)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
-        </is>
-      </c>
-      <c r="B18" s="128" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C18" s="129" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="130" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="E18" s="136" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
-        </is>
-      </c>
-      <c r="F18" s="132" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="G18" s="133">
-        <f>IF(F18="",0,C18*F18*10)</f>
-        <v/>
-      </c>
-      <c r="H18" s="134" t="inlineStr">
-        <is>
-          <t>3.2x</t>
+          <t>Rev growth σ=8.2%  |  OM trend -24.6%, σ=10.9%  [quality = direction + stability]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="n"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="136" t="inlineStr">
+        <is>
+          <t>TOTAL SCORE  (max = 100.0)</t>
+        </is>
+      </c>
+      <c r="B18" s="137" t="n"/>
+      <c r="C18" s="137" t="n"/>
+      <c r="D18" s="137" t="n"/>
+      <c r="E18" s="137" t="n"/>
+      <c r="F18" s="137" t="n"/>
+      <c r="G18" s="138">
+        <f>G8+G9+G10+G11+G13+G15+G16</f>
+        <v/>
+      </c>
+      <c r="H18" s="139" t="inlineStr">
+        <is>
+          <t>Floor cap 86.9 applies — see gate warning above.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interest Cover  (EBIT / Interest)</t>
-        </is>
-      </c>
-      <c r="B19" s="128" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C19" s="129" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="D19" s="130" t="inlineStr">
-        <is>
-          <t>0.0x</t>
-        </is>
-      </c>
-      <c r="E19" s="131" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F19" s="132" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G19" s="133">
-        <f>IF(F19="",0,C19*F19*10)</f>
-        <v/>
-      </c>
-      <c r="H19" s="134" t="inlineStr">
-        <is>
-          <t>0.0x</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Execution Risk</t>
-        </is>
-      </c>
-      <c r="B20" s="128" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C20" s="129" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D20" s="130" t="inlineStr">
-        <is>
-          <t>Rev growth σ=8.2%  |  Op margin σ=10.9%  [proxy — lower σ = lower risk = higher score]</t>
-        </is>
-      </c>
-      <c r="E20" s="136" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
-        </is>
-      </c>
-      <c r="F20" s="132" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="G20" s="133">
-        <f>IF(F20="",0,C20*F20*10)</f>
-        <v/>
-      </c>
-      <c r="H20" s="134" t="inlineStr">
-        <is>
-          <t>Rev growth σ=8.2%  |  Op margin σ=10.9%  [proxy — lower σ = lower risk = higher score]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>PART 4 — VALUATION  (qualitative / user-supplied market data)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Valuation vs Median  (P/E)</t>
-        </is>
-      </c>
-      <c r="B22" s="128" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C22" s="129" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D22" s="130" t="inlineStr">
-        <is>
-          <t>Current -658.4x — P/E negative (earnings/FCF below zero, multiple meaningless)</t>
-        </is>
-      </c>
-      <c r="E22" s="131" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F22" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="133">
-        <f>IF(F22="",0,C22*F22*10)</f>
-        <v/>
-      </c>
-      <c r="H22" s="134" t="inlineStr">
-        <is>
-          <t>Current -658.4x — P/E negative (earnings/FCF below zero, multiple meaningless)</t>
-        </is>
-      </c>
+      <c r="A19" s="140" t="inlineStr">
+        <is>
+          <t>FLOOR-ADJUSTED SCORE  (capped at 86.9)</t>
+        </is>
+      </c>
+      <c r="B19" s="141" t="n"/>
+      <c r="C19" s="141" t="n"/>
+      <c r="D19" s="141" t="n"/>
+      <c r="E19" s="141" t="n"/>
+      <c r="F19" s="141" t="n"/>
+      <c r="G19" s="142">
+        <f>MIN(G18,86.9)</f>
+        <v/>
+      </c>
+      <c r="H19" s="141" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="42" t="n"/>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="143">
+        <f>IF(G19="","Score incomplete — fill qualitative tiers above",IF(G19&gt;=80,"STRONG BUY",IF(G19&gt;=65,"BUY",IF(G19&gt;=50,"HOLD",IF(G19&gt;=35,"REDUCE","SELL")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Valuation vs Median  (P/FCF)</t>
-        </is>
-      </c>
-      <c r="B23" s="128" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C23" s="129" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D23" s="130" t="inlineStr">
-        <is>
-          <t>Current -35.5x — P/FCF negative (earnings/FCF below zero, multiple meaningless)</t>
-        </is>
-      </c>
-      <c r="E23" s="131" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F23" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="133">
-        <f>IF(F23="",0,C23*F23*10)</f>
-        <v/>
-      </c>
-      <c r="H23" s="134" t="inlineStr">
-        <is>
-          <t>Current -35.5x — P/FCF negative (earnings/FCF below zero, multiple meaningless)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="42" t="n"/>
-      <c r="B24" s="42" t="n"/>
-      <c r="C24" s="42" t="n"/>
-      <c r="D24" s="42" t="n"/>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="42" t="n"/>
-      <c r="G24" s="42" t="n"/>
-      <c r="H24" s="42" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="137" t="inlineStr">
-        <is>
-          <t>TOTAL SCORE  (max = 100.0)</t>
-        </is>
-      </c>
-      <c r="B25" s="138" t="n"/>
-      <c r="C25" s="138" t="n"/>
-      <c r="D25" s="138" t="n"/>
-      <c r="E25" s="138" t="n"/>
-      <c r="F25" s="138" t="n"/>
-      <c r="G25" s="139">
-        <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
-        <v/>
-      </c>
-      <c r="H25" s="140" t="inlineStr">
-        <is>
-          <t>Floor cap 86.9 applies — see gate warning above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="141" t="inlineStr">
-        <is>
-          <t>FLOOR-ADJUSTED SCORE  (capped at 86.9)</t>
-        </is>
-      </c>
-      <c r="B26" s="142" t="n"/>
-      <c r="C26" s="142" t="n"/>
-      <c r="D26" s="142" t="n"/>
-      <c r="E26" s="142" t="n"/>
-      <c r="F26" s="142" t="n"/>
-      <c r="G26" s="143">
-        <f>MIN(G25,86.9)</f>
-        <v/>
-      </c>
-      <c r="H26" s="142" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="42" t="n"/>
-      <c r="B27" s="42" t="n"/>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
-      <c r="F27" s="42" t="n"/>
-      <c r="G27" s="42" t="n"/>
-      <c r="H27" s="42" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="144">
-        <f>IF(G26="","Score incomplete — fill qualitative tiers above",IF(G26&gt;=80,"STRONG BUY",IF(G26&gt;=65,"BUY",IF(G26&gt;=50,"HOLD",IF(G26&gt;=35,"REDUCE","SELL")))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="42" t="n"/>
-      <c r="B29" s="42" t="n"/>
-      <c r="C29" s="42" t="n"/>
-      <c r="D29" s="42" t="n"/>
-      <c r="E29" s="42" t="n"/>
-      <c r="F29" s="42" t="n"/>
-      <c r="G29" s="42" t="n"/>
-      <c r="H29" s="42" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="145" t="inlineStr">
+      <c r="A23" s="144" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E9:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/static/excel/INTC_model.xlsx
+++ b/static/excel/INTC_model.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="175" formatCode="0.000"/>
     <numFmt numFmtId="176" formatCode="0.00;(0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -223,6 +223,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00E65100"/>
       <sz val="10"/>
     </font>
@@ -238,7 +244,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -335,6 +341,11 @@
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -362,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -758,7 +769,10 @@
     <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -771,17 +785,17 @@
     <xf numFmtId="0" fontId="30" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="32" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="33" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -7425,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7661,25 +7675,27 @@
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B34" s="54" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="n">
+        <v>0.0539</v>
+      </c>
       <c r="C34" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A4CBBBEY — BBB</t>
         </is>
       </c>
     </row>
@@ -7722,11 +7738,11 @@
         </is>
       </c>
       <c r="B37" s="46" t="n">
-        <v>0.1657</v>
+        <v>0.1656</v>
       </c>
       <c r="C37" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 12.00%</t>
+          <t>Rf 4.56% + spread 12.00%</t>
         </is>
       </c>
     </row>
@@ -7752,11 +7768,11 @@
         </is>
       </c>
       <c r="B39" s="48" t="n">
-        <v>0.0941</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -9445,7 +9461,7 @@
       <c r="L37" s="99" t="n"/>
       <c r="M37" s="75" t="inlineStr">
         <is>
-          <t>Growth tier: LOW (-5.5% 3yr avg rev growth).  Bear 2.00% / Base 2.5% / Bull 3.00%.  Keep below WACC.</t>
+          <t>Growth tier: LOW (-8.0% 3yr avg rev growth).  Bear 2.00% / Base 2.5% / Bull 3.00%.  Keep below WACC.</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9486,7 @@
       <c r="L38" s="99" t="n"/>
       <c r="M38" s="75" t="inlineStr">
         <is>
-          <t>Growth tier: LOW (-5.5% 3yr avg rev growth).  Bear 8x / Base 10x / Bull 12x.  Override manually if needed.</t>
+          <t>Growth tier: LOW (-8.0% 3yr avg rev growth).  Bear 8x / Base 10x / Bull 12x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10072,7 +10088,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — INTC  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — INTC  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10187,7 @@
         </is>
       </c>
       <c r="C8" s="121" t="n">
-        <v>0.075</v>
+        <v>0.025</v>
       </c>
       <c r="D8" s="122" t="inlineStr">
         <is>
@@ -10201,11 +10217,11 @@
         </is>
       </c>
       <c r="C9" s="129" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D9" s="130" t="inlineStr">
         <is>
-          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -13.1% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
+          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -13.2% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="131" t="inlineStr">
@@ -10222,7 +10238,7 @@
       </c>
       <c r="H9" s="134" t="inlineStr">
         <is>
-          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -13.1% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
+          <t>GM 34.8% ✗ (&gt;40%)  |  GM trend -7.8% ✗ (&gt;+1pp)  |  ROIC-WACC -13.2% ✗ (&gt;+5pp)  |  Rev consistency σ=8.2% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10254,7 @@
         </is>
       </c>
       <c r="C10" s="121" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="D10" s="122" t="inlineStr">
         <is>
@@ -10268,7 +10284,7 @@
         </is>
       </c>
       <c r="C11" s="129" t="n">
-        <v>0.125</v>
+        <v>0.075</v>
       </c>
       <c r="D11" s="130" t="inlineStr">
         <is>
@@ -10312,7 +10328,7 @@
         </is>
       </c>
       <c r="C13" s="129" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="130" t="inlineStr">
         <is>
@@ -10338,21 +10354,51 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>PART 3 — RISK PROFILE  (quantitative / qualitative)</t>
+      <c r="A14" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash Quality  (FCF / Net Income)</t>
+        </is>
+      </c>
+      <c r="B14" s="128" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C14" s="129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D14" s="130" t="inlineStr">
+        <is>
+          <t>1311%  [through-cycle: 70/30 latest+5yr median, latest 1853.6% → smoothed 1311.3%]</t>
+        </is>
+      </c>
+      <c r="E14" s="135" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F14" s="132" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="133">
+        <f>IF(F14="",0,C14*F14*10)</f>
+        <v/>
+      </c>
+      <c r="H14" s="134" t="inlineStr">
+        <is>
+          <t>1311%  [through-cycle: 70/30 latest+5yr median, latest 1853.6% → smoothed 1311.3%]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
+          <t xml:space="preserve">  Capital Returns</t>
         </is>
       </c>
       <c r="B15" s="128" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C15" s="129" t="n">
@@ -10360,16 +10406,16 @@
       </c>
       <c r="D15" s="130" t="inlineStr">
         <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="E15" s="135" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
+          <t>No capital returns in latest year</t>
+        </is>
+      </c>
+      <c r="E15" s="131" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F15" s="132" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="G15" s="133">
         <f>IF(F15="",0,C15*F15*10)</f>
@@ -10377,36 +10423,36 @@
       </c>
       <c r="H15" s="134" t="inlineStr">
         <is>
-          <t>3.2x</t>
+          <t>No capital returns in latest year</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Execution Risk</t>
+          <t xml:space="preserve">  ROIC</t>
         </is>
       </c>
       <c r="B16" s="128" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C16" s="129" t="n">
-        <v>0.05</v>
+        <v>0.075</v>
       </c>
       <c r="D16" s="130" t="inlineStr">
         <is>
-          <t>Rev growth σ=8.2%  |  OM trend -24.6%, σ=10.9%  [quality = direction + stability]</t>
-        </is>
-      </c>
-      <c r="E16" s="135" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
+          <t>0.5%  [through-cycle: 70/30 latest+5yr median, latest 0.0% → smoothed 0.5%]  [QoE: CFO/NI -999% 3yr avg — cash conv weak]</t>
+        </is>
+      </c>
+      <c r="E16" s="131" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F16" s="132" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="G16" s="133">
         <f>IF(F16="",0,C16*F16*10)</f>
@@ -10414,101 +10460,294 @@
       </c>
       <c r="H16" s="134" t="inlineStr">
         <is>
+          <t>0.5%  [through-cycle: 70/30 latest+5yr median, latest 0.0% → smoothed 0.5%]  [QoE: CFO/NI -999% 3yr avg — cash conv weak]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>PART 3 — RISK PROFILE  (quantitative / qualitative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
+        </is>
+      </c>
+      <c r="B18" s="128" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C18" s="129" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D18" s="130" t="inlineStr">
+        <is>
+          <t>3.2x</t>
+        </is>
+      </c>
+      <c r="E18" s="136" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
+        </is>
+      </c>
+      <c r="F18" s="132" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="G18" s="133">
+        <f>IF(F18="",0,C18*F18*10)</f>
+        <v/>
+      </c>
+      <c r="H18" s="134" t="inlineStr">
+        <is>
+          <t>3.2x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest Cover  (EBIT / Interest)</t>
+        </is>
+      </c>
+      <c r="B19" s="128" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C19" s="129" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D19" s="130" t="inlineStr">
+        <is>
+          <t>0.0x</t>
+        </is>
+      </c>
+      <c r="E19" s="131" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F19" s="132" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G19" s="133">
+        <f>IF(F19="",0,C19*F19*10)</f>
+        <v/>
+      </c>
+      <c r="H19" s="134" t="inlineStr">
+        <is>
+          <t>0.0x</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Execution Risk</t>
+        </is>
+      </c>
+      <c r="B20" s="128" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C20" s="129" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D20" s="130" t="inlineStr">
+        <is>
           <t>Rev growth σ=8.2%  |  OM trend -24.6%, σ=10.9%  [quality = direction + stability]</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="n"/>
-      <c r="B17" s="42" t="n"/>
-      <c r="C17" s="42" t="n"/>
-      <c r="D17" s="42" t="n"/>
-      <c r="E17" s="42" t="n"/>
-      <c r="F17" s="42" t="n"/>
-      <c r="G17" s="42" t="n"/>
-      <c r="H17" s="42" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="136" t="inlineStr">
+      <c r="E20" s="136" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
+        </is>
+      </c>
+      <c r="F20" s="132" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="G20" s="133">
+        <f>IF(F20="",0,C20*F20*10)</f>
+        <v/>
+      </c>
+      <c r="H20" s="134" t="inlineStr">
+        <is>
+          <t>Rev growth σ=8.2%  |  OM trend -24.6%, σ=10.9%  [quality = direction + stability]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>PART 4 — VALUATION  (qualitative / user-supplied market data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Valuation vs Median  (P/E)</t>
+        </is>
+      </c>
+      <c r="B22" s="128" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C22" s="129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="130" t="inlineStr">
+        <is>
+          <t>Fwd P/E 111.3x (scoring basis)  |  5yr avg 49.6x  |  Sector median 80.5x  [+124% vs benchmark]  [trail=0.00 | fwd_pe=111.3x→0.00 | abs=0.0 → blended 40/40/20=0.00]</t>
+        </is>
+      </c>
+      <c r="E22" s="131" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F22" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="133">
+        <f>IF(F22="",0,C22*F22*10)</f>
+        <v/>
+      </c>
+      <c r="H22" s="134" t="inlineStr">
+        <is>
+          <t>Fwd P/E 111.3x (scoring basis)  |  5yr avg 49.6x  |  Sector median 80.5x  [+124% vs benchmark]  [trail=0.00 | fwd_pe=111.3x→0.00 | abs=0.0 → blended 40/40/20=0.00]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Valuation vs Median  (P/FCF)</t>
+        </is>
+      </c>
+      <c r="B23" s="120" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C23" s="121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="122" t="inlineStr">
+        <is>
+          <t>— user input required</t>
+        </is>
+      </c>
+      <c r="E23" s="123" t="n"/>
+      <c r="F23" s="124">
+        <f>IF(E23="HIGH",10,IF(E23="MOD-HIGH",7,IF(E23="MOD-LOW",3,IF(E23="LOW",0,""))))</f>
+        <v/>
+      </c>
+      <c r="G23" s="125">
+        <f>IF(F23="",0,C23*F23*10)</f>
+        <v/>
+      </c>
+      <c r="H23" s="126" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="42" t="n"/>
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="42" t="n"/>
+      <c r="G24" s="42" t="n"/>
+      <c r="H24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="137" t="inlineStr">
         <is>
           <t>TOTAL SCORE  (max = 100.0)</t>
         </is>
       </c>
-      <c r="B18" s="137" t="n"/>
-      <c r="C18" s="137" t="n"/>
-      <c r="D18" s="137" t="n"/>
-      <c r="E18" s="137" t="n"/>
-      <c r="F18" s="137" t="n"/>
-      <c r="G18" s="138">
-        <f>G8+G9+G10+G11+G13+G15+G16</f>
-        <v/>
-      </c>
-      <c r="H18" s="139" t="inlineStr">
+      <c r="B25" s="138" t="n"/>
+      <c r="C25" s="138" t="n"/>
+      <c r="D25" s="138" t="n"/>
+      <c r="E25" s="138" t="n"/>
+      <c r="F25" s="138" t="n"/>
+      <c r="G25" s="139">
+        <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
+        <v/>
+      </c>
+      <c r="H25" s="140" t="inlineStr">
         <is>
           <t>Floor cap 86.9 applies — see gate warning above.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="140" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="141" t="inlineStr">
         <is>
           <t>FLOOR-ADJUSTED SCORE  (capped at 86.9)</t>
         </is>
       </c>
-      <c r="B19" s="141" t="n"/>
-      <c r="C19" s="141" t="n"/>
-      <c r="D19" s="141" t="n"/>
-      <c r="E19" s="141" t="n"/>
-      <c r="F19" s="141" t="n"/>
-      <c r="G19" s="142">
-        <f>MIN(G18,86.9)</f>
-        <v/>
-      </c>
-      <c r="H19" s="141" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="42" t="n"/>
-      <c r="B20" s="42" t="n"/>
-      <c r="C20" s="42" t="n"/>
-      <c r="D20" s="42" t="n"/>
-      <c r="E20" s="42" t="n"/>
-      <c r="F20" s="42" t="n"/>
-      <c r="G20" s="42" t="n"/>
-      <c r="H20" s="42" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="143">
-        <f>IF(G19="","Score incomplete — fill qualitative tiers above",IF(G19&gt;=80,"STRONG BUY",IF(G19&gt;=65,"BUY",IF(G19&gt;=50,"HOLD",IF(G19&gt;=35,"REDUCE","SELL")))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="n"/>
-      <c r="B22" s="42" t="n"/>
-      <c r="C22" s="42" t="n"/>
-      <c r="D22" s="42" t="n"/>
-      <c r="E22" s="42" t="n"/>
-      <c r="F22" s="42" t="n"/>
-      <c r="G22" s="42" t="n"/>
-      <c r="H22" s="42" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="144" t="inlineStr">
+      <c r="B26" s="142" t="n"/>
+      <c r="C26" s="142" t="n"/>
+      <c r="D26" s="142" t="n"/>
+      <c r="E26" s="142" t="n"/>
+      <c r="F26" s="142" t="n"/>
+      <c r="G26" s="143">
+        <f>MIN(G25,86.9)</f>
+        <v/>
+      </c>
+      <c r="H26" s="142" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="42" t="n"/>
+      <c r="C27" s="42" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="42" t="n"/>
+      <c r="G27" s="42" t="n"/>
+      <c r="H27" s="42" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="144">
+        <f>IF(G26="","Score incomplete — fill qualitative tiers above",IF(G26&gt;=80,"STRONG BUY",IF(G26&gt;=65,"BUY",IF(G26&gt;=50,"HOLD",IF(G26&gt;=35,"REDUCE","SELL")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="n"/>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="42" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="42" t="n"/>
+      <c r="G29" s="42" t="n"/>
+      <c r="H29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="145" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E9:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
